--- a/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
+++ b/products/reseller-free-calculator/Reseller_Profit_After_Fees_Calculator_2026.xlsx
@@ -253,16 +253,16 @@
     <t xml:space="preserve">Depop</t>
   </si>
   <si>
-    <t xml:space="preserve">not re-verified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US selling fee moved to the buyer; roughly 3.3% + $0.45 payment processing remains on the seller. Verify for your region before trusting this row.</t>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No US selling commission since 2024 - it moved to the buyer. What remains on the seller is 3.3% + $0.45 payment processing, charged on item + shipping + tax. An optional Boosted Listing costs 12% on top if you use one; this row does not include it.</t>
   </si>
   <si>
     <t xml:space="preserve">Facebook Marketplace</t>
   </si>
   <si>
-    <t xml:space="preserve">About 5% of the total on shipped orders, with a minimum around $0.40. Local pickup is normally free. Verify before trusting this row.</t>
+    <t xml:space="preserve">10% of the buyer's total (item + the shipping you charge + the sales tax Meta collects), minimum $0.80 per order. Raised from 5% / $0.40 on 15 April 2024. Local pickup sales have no selling fee at all - price those with the 'Other' row set to 0%.</t>
   </si>
   <si>
     <t xml:space="preserve">Other / edit me</t>
@@ -313,7 +313,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,14 +466,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -544,7 +536,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -655,10 +647,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -1361,7 +1349,7 @@
       </c>
       <c r="H15" s="16" t="str">
         <f aca="false">Fees!$K$7</f>
-        <v>not re-verified</v>
+        <v>2026-09-11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1371,15 +1359,15 @@
       </c>
       <c r="B16" s="13" t="n">
         <f aca="false">MAX(IF(AND(Fees!$H$8&gt;0,$B$5&lt;Fees!$H$8),Fees!$I$8,($B$5+IF(Fees!$G$8="Y",$B$6,0))*Fees!$B$8+IF(AND(Fees!$E$8&gt;0,$B$5&lt;=Fees!$E$8),Fees!$D$8,Fees!$C$8)+($B$5+IF(Fees!$G$8="Y",$B$6,0))*Fees!$F$8),Fees!$J$8)</f>
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">IF(($B$5+$B$6)&lt;=0,"-",B16/($B$5+$B$6))</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D16" s="13" t="n">
         <f aca="false">$B$5+$B$6-B16</f>
-        <v>42.75</v>
+        <v>40.5</v>
       </c>
       <c r="E16" s="13" t="n">
         <f aca="false">($B$4+$B$7+$B$8)</f>
@@ -1387,15 +1375,15 @@
       </c>
       <c r="F16" s="15" t="n">
         <f aca="false">D16-E16</f>
-        <v>23.75</v>
+        <v>21.5</v>
       </c>
       <c r="G16" s="14" t="n">
         <f aca="false">IF(($B$4+$B$7+$B$8)&lt;=0,"-",F16/($B$4+$B$7+$B$8))</f>
-        <v>1.25</v>
+        <v>1.13157894736842</v>
       </c>
       <c r="H16" s="16" t="str">
         <f aca="false">Fees!$K$8</f>
-        <v>not re-verified</v>
+        <v>2026-09-11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1700,7 +1688,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>75</v>
       </c>
@@ -1731,7 +1719,7 @@
       <c r="J7" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="28" t="s">
+      <c r="K7" s="26" t="s">
         <v>76</v>
       </c>
       <c r="L7" s="27" t="s">
@@ -1743,7 +1731,7 @@
         <v>78</v>
       </c>
       <c r="B8" s="23" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0</v>
@@ -1767,9 +1755,9 @@
         <v>0</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K8" s="28" t="s">
+        <v>0.8</v>
+      </c>
+      <c r="K8" s="26" t="s">
         <v>76</v>
       </c>
       <c r="L8" s="27" t="s">
@@ -1918,7 +1906,7 @@
         <f aca="false">IF($B4="","",$D4+$E4-$H4)</f>
         <v>38.48</v>
       </c>
-      <c r="J4" s="29" t="n">
+      <c r="J4" s="28" t="n">
         <f aca="false">IF($B4="","",$I4-($C4+$F4+$G4))</f>
         <v>19.48</v>
       </c>
@@ -1943,7 +1931,7 @@
         <f aca="false">IF($B5="","",$D5+$E5-$H5)</f>
         <v/>
       </c>
-      <c r="J5" s="29" t="str">
+      <c r="J5" s="28" t="str">
         <f aca="false">IF($B5="","",$I5-($C5+$F5+$G5))</f>
         <v/>
       </c>
@@ -1968,7 +1956,7 @@
         <f aca="false">IF($B6="","",$D6+$E6-$H6)</f>
         <v/>
       </c>
-      <c r="J6" s="29" t="str">
+      <c r="J6" s="28" t="str">
         <f aca="false">IF($B6="","",$I6-($C6+$F6+$G6))</f>
         <v/>
       </c>
@@ -1993,7 +1981,7 @@
         <f aca="false">IF($B7="","",$D7+$E7-$H7)</f>
         <v/>
       </c>
-      <c r="J7" s="29" t="str">
+      <c r="J7" s="28" t="str">
         <f aca="false">IF($B7="","",$I7-($C7+$F7+$G7))</f>
         <v/>
       </c>
@@ -2018,7 +2006,7 @@
         <f aca="false">IF($B8="","",$D8+$E8-$H8)</f>
         <v/>
       </c>
-      <c r="J8" s="29" t="str">
+      <c r="J8" s="28" t="str">
         <f aca="false">IF($B8="","",$I8-($C8+$F8+$G8))</f>
         <v/>
       </c>
@@ -2043,7 +2031,7 @@
         <f aca="false">IF($B9="","",$D9+$E9-$H9)</f>
         <v/>
       </c>
-      <c r="J9" s="29" t="str">
+      <c r="J9" s="28" t="str">
         <f aca="false">IF($B9="","",$I9-($C9+$F9+$G9))</f>
         <v/>
       </c>
@@ -2068,7 +2056,7 @@
         <f aca="false">IF($B10="","",$D10+$E10-$H10)</f>
         <v/>
       </c>
-      <c r="J10" s="29" t="str">
+      <c r="J10" s="28" t="str">
         <f aca="false">IF($B10="","",$I10-($C10+$F10+$G10))</f>
         <v/>
       </c>
@@ -2093,7 +2081,7 @@
         <f aca="false">IF($B11="","",$D11+$E11-$H11)</f>
         <v/>
       </c>
-      <c r="J11" s="29" t="str">
+      <c r="J11" s="28" t="str">
         <f aca="false">IF($B11="","",$I11-($C11+$F11+$G11))</f>
         <v/>
       </c>
@@ -2118,7 +2106,7 @@
         <f aca="false">IF($B12="","",$D12+$E12-$H12)</f>
         <v/>
       </c>
-      <c r="J12" s="29" t="str">
+      <c r="J12" s="28" t="str">
         <f aca="false">IF($B12="","",$I12-($C12+$F12+$G12))</f>
         <v/>
       </c>
@@ -2143,7 +2131,7 @@
         <f aca="false">IF($B13="","",$D13+$E13-$H13)</f>
         <v/>
       </c>
-      <c r="J13" s="29" t="str">
+      <c r="J13" s="28" t="str">
         <f aca="false">IF($B13="","",$I13-($C13+$F13+$G13))</f>
         <v/>
       </c>
@@ -2168,7 +2156,7 @@
         <f aca="false">IF($B14="","",$D14+$E14-$H14)</f>
         <v/>
       </c>
-      <c r="J14" s="29" t="str">
+      <c r="J14" s="28" t="str">
         <f aca="false">IF($B14="","",$I14-($C14+$F14+$G14))</f>
         <v/>
       </c>
@@ -2193,7 +2181,7 @@
         <f aca="false">IF($B15="","",$D15+$E15-$H15)</f>
         <v/>
       </c>
-      <c r="J15" s="29" t="str">
+      <c r="J15" s="28" t="str">
         <f aca="false">IF($B15="","",$I15-($C15+$F15+$G15))</f>
         <v/>
       </c>
@@ -2218,7 +2206,7 @@
         <f aca="false">IF($B16="","",$D16+$E16-$H16)</f>
         <v/>
       </c>
-      <c r="J16" s="29" t="str">
+      <c r="J16" s="28" t="str">
         <f aca="false">IF($B16="","",$I16-($C16+$F16+$G16))</f>
         <v/>
       </c>
@@ -2243,7 +2231,7 @@
         <f aca="false">IF($B17="","",$D17+$E17-$H17)</f>
         <v/>
       </c>
-      <c r="J17" s="29" t="str">
+      <c r="J17" s="28" t="str">
         <f aca="false">IF($B17="","",$I17-($C17+$F17+$G17))</f>
         <v/>
       </c>
@@ -2268,7 +2256,7 @@
         <f aca="false">IF($B18="","",$D18+$E18-$H18)</f>
         <v/>
       </c>
-      <c r="J18" s="29" t="str">
+      <c r="J18" s="28" t="str">
         <f aca="false">IF($B18="","",$I18-($C18+$F18+$G18))</f>
         <v/>
       </c>
@@ -2293,7 +2281,7 @@
         <f aca="false">IF($B19="","",$D19+$E19-$H19)</f>
         <v/>
       </c>
-      <c r="J19" s="29" t="str">
+      <c r="J19" s="28" t="str">
         <f aca="false">IF($B19="","",$I19-($C19+$F19+$G19))</f>
         <v/>
       </c>
@@ -2318,7 +2306,7 @@
         <f aca="false">IF($B20="","",$D20+$E20-$H20)</f>
         <v/>
       </c>
-      <c r="J20" s="29" t="str">
+      <c r="J20" s="28" t="str">
         <f aca="false">IF($B20="","",$I20-($C20+$F20+$G20))</f>
         <v/>
       </c>
@@ -2343,7 +2331,7 @@
         <f aca="false">IF($B21="","",$D21+$E21-$H21)</f>
         <v/>
       </c>
-      <c r="J21" s="29" t="str">
+      <c r="J21" s="28" t="str">
         <f aca="false">IF($B21="","",$I21-($C21+$F21+$G21))</f>
         <v/>
       </c>
@@ -2368,7 +2356,7 @@
         <f aca="false">IF($B22="","",$D22+$E22-$H22)</f>
         <v/>
       </c>
-      <c r="J22" s="29" t="str">
+      <c r="J22" s="28" t="str">
         <f aca="false">IF($B22="","",$I22-($C22+$F22+$G22))</f>
         <v/>
       </c>
@@ -2393,7 +2381,7 @@
         <f aca="false">IF($B23="","",$D23+$E23-$H23)</f>
         <v/>
       </c>
-      <c r="J23" s="29" t="str">
+      <c r="J23" s="28" t="str">
         <f aca="false">IF($B23="","",$I23-($C23+$F23+$G23))</f>
         <v/>
       </c>
@@ -2406,7 +2394,7 @@
       <c r="A25" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="J25" s="30" t="n">
+      <c r="J25" s="29" t="n">
         <f aca="false">SUM(J4:J23)</f>
         <v>19.48</v>
       </c>
